--- a/STROKE_form_labtests.xlsx
+++ b/STROKE_form_labtests.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wrk\phd\HIS_Forms_for_Stroke_Care\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EE369D-6390-4F22-9A75-6B6499D2FB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -127,8 +133,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,7 +159,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -176,28 +182,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -235,7 +264,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -269,6 +298,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -303,9 +333,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -478,11 +509,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.3828125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="22.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.4609375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.3046875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,8 +537,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
@@ -513,7 +551,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="3"/>
       <c r="B3" t="s">
         <v>8</v>
       </c>
@@ -521,7 +560,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="3"/>
       <c r="B4" t="s">
         <v>9</v>
       </c>
@@ -532,7 +572,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="3"/>
       <c r="B5" t="s">
         <v>10</v>
       </c>
@@ -543,7 +584,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="3"/>
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -554,7 +596,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="3"/>
       <c r="B7" t="s">
         <v>12</v>
       </c>
@@ -565,7 +608,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="3"/>
       <c r="B8" t="s">
         <v>13</v>
       </c>
@@ -576,7 +620,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" s="3"/>
       <c r="B9" t="s">
         <v>14</v>
       </c>
@@ -587,7 +632,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" s="3"/>
       <c r="B10" t="s">
         <v>15</v>
       </c>
@@ -598,7 +644,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" s="3"/>
       <c r="B11" t="s">
         <v>16</v>
       </c>
@@ -609,7 +656,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" s="3"/>
       <c r="B12" t="s">
         <v>17</v>
       </c>
@@ -620,7 +668,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" s="3"/>
       <c r="B13" t="s">
         <v>18</v>
       </c>
@@ -631,7 +680,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" s="3"/>
       <c r="B14" t="s">
         <v>19</v>
       </c>
@@ -642,7 +692,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" s="3"/>
       <c r="B15" t="s">
         <v>20</v>
       </c>
@@ -653,8 +704,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B16" t="s">
@@ -667,7 +718,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A17" s="3"/>
       <c r="B17" t="s">
         <v>22</v>
       </c>
@@ -678,7 +730,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" s="3"/>
       <c r="B18" t="s">
         <v>23</v>
       </c>
@@ -686,7 +739,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="2:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A19" s="3"/>
       <c r="B19" t="s">
         <v>24</v>
       </c>
@@ -698,6 +752,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>